--- a/artfynd/A 476-2025 artfynd.xlsx
+++ b/artfynd/A 476-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -817,6 +817,621 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122005426</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57985</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102125</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tallbit</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pinicola enucleator</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>364842</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6626908</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Gunnarskog</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Grupp med tallbitar i trädkronorna.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Isabel Gunn</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Isabel Gunn</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122008463</v>
+      </c>
+      <c r="B4" t="n">
+        <v>74674</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>364847</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6626801</v>
+      </c>
+      <c r="S4" t="n">
+        <v>9</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gunnarskog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122006954</v>
+      </c>
+      <c r="B5" t="n">
+        <v>74674</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Pers stuga, Pers stuga, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>364824</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6626976</v>
+      </c>
+      <c r="S5" t="n">
+        <v>9</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gunnarskog</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Växer på flera träd i området</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122008545</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57381</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>364842</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6626782</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gunnarskog</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122009276</v>
+      </c>
+      <c r="B7" t="n">
+        <v>74674</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Pers stuga, Pers stuga, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>364755</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6626989</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gunnarskog</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 476-2025 artfynd.xlsx
+++ b/artfynd/A 476-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -820,10 +820,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122005426</v>
+        <v>122006954</v>
       </c>
       <c r="B3" t="n">
-        <v>57985</v>
+        <v>74674</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,41 +832,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102125</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
+          <t>Pers stuga, Pers stuga, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>364842</v>
+        <v>364824</v>
       </c>
       <c r="R3" t="n">
-        <v>6626908</v>
+        <v>6626976</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Grupp med tallbitar i trädkronorna.</t>
+          <t>Växer på flera träd i området</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,23 +921,43 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122008463</v>
+        <v>122009276</v>
       </c>
       <c r="B4" t="n">
         <v>74674</v>
@@ -973,17 +993,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
+          <t>Pers stuga, Pers stuga, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>364847</v>
+        <v>364755</v>
       </c>
       <c r="R4" t="n">
-        <v>6626801</v>
+        <v>6626989</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,7 +1042,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,31 +1053,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1074,7 +1069,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122006954</v>
+        <v>122008463</v>
       </c>
       <c r="B5" t="n">
         <v>74674</v>
@@ -1110,14 +1105,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Pers stuga, Pers stuga, Vrm</t>
+          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>364824</v>
+        <v>364847</v>
       </c>
       <c r="R5" t="n">
-        <v>6626976</v>
+        <v>6626801</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1149,7 +1144,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1159,12 +1154,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Växer på flera träd i området</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1176,6 +1166,11 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
       <c r="AJ5" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1188,12 +1183,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1323,10 +1318,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122009276</v>
+        <v>122022549</v>
       </c>
       <c r="B7" t="n">
-        <v>74674</v>
+        <v>74727</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1335,38 +1330,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Pers stuga, Pers stuga, Vrm</t>
+          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>364755</v>
+        <v>364852</v>
       </c>
       <c r="R7" t="n">
-        <v>6626989</v>
+        <v>6626722</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1396,19 +1391,14 @@
           <t>2025-01-09</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-09</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:29</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flera torrrakor i området med förekomst av spiklavar. Blir osäker om artbestämningen. Kan vara  litenspiklav eller svartspiklav</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1423,15 +1413,366 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Isabel Gunn</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Isabel Gunn</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122022112</v>
+      </c>
+      <c r="B8" t="n">
+        <v>74674</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>364799</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6626930</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gunnarskog</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Förekomst av kattfotslav på flera av gammal granarna, ofta i samband med gammelgranslav.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Isabel Gunn</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Isabel Gunn</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122025041</v>
+      </c>
+      <c r="B9" t="n">
+        <v>96398</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Pers stuga, Pers stuga, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>364825</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6626868</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gunnarskog</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Växer på de flesta bergsväggarna i området.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Petrus Oledal</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Petrus Oledal</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122025014</v>
+      </c>
+      <c r="B10" t="n">
+        <v>96398</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Pers stuga, Pers stuga, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>364791</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6627003</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gunnarskog</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-01-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Växer på dom flesta bergväggarna i området</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Petrus Oledal</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 476-2025 artfynd.xlsx
+++ b/artfynd/A 476-2025 artfynd.xlsx
@@ -1425,10 +1425,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122022112</v>
+        <v>122025014</v>
       </c>
       <c r="B8" t="n">
-        <v>74674</v>
+        <v>96398</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1441,37 +1441,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6426</v>
+        <v>2569</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
+          <t>Pers stuga, Pers stuga, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>364799</v>
+        <v>364791</v>
       </c>
       <c r="R8" t="n">
-        <v>6626930</v>
+        <v>6627003</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1498,14 +1498,24 @@
           <t>2025-01-09</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-09</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Förekomst av kattfotslav på flera av gammal granarna, ofta i samband med gammelgranslav.</t>
+          <t>Växer på dom flesta bergväggarna i området</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1516,26 +1526,36 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122025041</v>
+        <v>122022112</v>
       </c>
       <c r="B9" t="n">
-        <v>96398</v>
+        <v>74674</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1548,37 +1568,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2569</v>
+        <v>6426</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Pers stuga, Pers stuga, Vrm</t>
+          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>364825</v>
+        <v>364799</v>
       </c>
       <c r="R9" t="n">
-        <v>6626868</v>
+        <v>6626930</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1605,24 +1625,14 @@
           <t>2025-01-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-01-09</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Växer på de flesta bergsväggarna i området.</t>
+          <t>Förekomst av kattfotslav på flera av gammal granarna, ofta i samband med gammelgranslav.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1637,19 +1647,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122025014</v>
+        <v>122025041</v>
       </c>
       <c r="B10" t="n">
         <v>96398</v>
@@ -1689,10 +1699,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>364791</v>
+        <v>364825</v>
       </c>
       <c r="R10" t="n">
-        <v>6627003</v>
+        <v>6626868</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1739,7 +1749,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Växer på dom flesta bergväggarna i området</t>
+          <t>Växer på de flesta bergsväggarna i området.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1750,16 +1760,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">

--- a/artfynd/A 476-2025 artfynd.xlsx
+++ b/artfynd/A 476-2025 artfynd.xlsx
@@ -823,7 +823,7 @@
         <v>122006954</v>
       </c>
       <c r="B3" t="n">
-        <v>74674</v>
+        <v>74676</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>122009276</v>
       </c>
       <c r="B4" t="n">
-        <v>74674</v>
+        <v>74676</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1069,10 +1069,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122008463</v>
+        <v>122008545</v>
       </c>
       <c r="B5" t="n">
-        <v>74674</v>
+        <v>57381</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1081,25 +1081,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1109,13 +1109,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>364847</v>
+        <v>364842</v>
       </c>
       <c r="R5" t="n">
-        <v>6626801</v>
+        <v>6626782</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1165,31 +1165,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1206,10 +1181,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122008545</v>
+        <v>122008463</v>
       </c>
       <c r="B6" t="n">
-        <v>57381</v>
+        <v>74676</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1218,25 +1193,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1246,13 +1221,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>364842</v>
+        <v>364847</v>
       </c>
       <c r="R6" t="n">
-        <v>6626782</v>
+        <v>6626801</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1281,7 +1256,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1291,7 +1266,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1302,6 +1277,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1318,10 +1318,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122022549</v>
+        <v>122025041</v>
       </c>
       <c r="B7" t="n">
-        <v>74727</v>
+        <v>96666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1330,41 +1330,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>308</v>
+        <v>2569</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
+          <t>Pers stuga, Pers stuga, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>364852</v>
+        <v>364825</v>
       </c>
       <c r="R7" t="n">
-        <v>6626722</v>
+        <v>6626868</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1391,14 +1391,24 @@
           <t>2025-01-09</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-09</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Flera torrrakor i området med förekomst av spiklavar. Blir osäker om artbestämningen. Kan vara  litenspiklav eller svartspiklav</t>
+          <t>Växer på de flesta bergsväggarna i området.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1413,22 +1423,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122025014</v>
+        <v>122022112</v>
       </c>
       <c r="B8" t="n">
-        <v>96398</v>
+        <v>74676</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1441,37 +1451,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2569</v>
+        <v>6426</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Pers stuga, Pers stuga, Vrm</t>
+          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>364791</v>
+        <v>364799</v>
       </c>
       <c r="R8" t="n">
-        <v>6627003</v>
+        <v>6626930</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1498,24 +1508,14 @@
           <t>2025-01-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-09</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Växer på dom flesta bergväggarna i området</t>
+          <t>Förekomst av kattfotslav på flera av gammal granarna, ofta i samband med gammelgranslav.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1526,36 +1526,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122022112</v>
+        <v>122022549</v>
       </c>
       <c r="B9" t="n">
-        <v>74674</v>
+        <v>74729</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1564,25 +1554,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6426</v>
+        <v>308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1592,10 +1582,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>364799</v>
+        <v>364852</v>
       </c>
       <c r="R9" t="n">
-        <v>6626930</v>
+        <v>6626722</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1632,7 +1622,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Förekomst av kattfotslav på flera av gammal granarna, ofta i samband med gammelgranslav.</t>
+          <t>Flera torrrakor i området med förekomst av spiklavar. Blir osäker om artbestämningen. Kan vara  litenspiklav eller svartspiklav</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1659,10 +1649,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122025041</v>
+        <v>122025014</v>
       </c>
       <c r="B10" t="n">
-        <v>96398</v>
+        <v>96666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1699,10 +1689,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>364825</v>
+        <v>364791</v>
       </c>
       <c r="R10" t="n">
-        <v>6626868</v>
+        <v>6627003</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1749,7 +1739,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Växer på de flesta bergsväggarna i området.</t>
+          <t>Växer på dom flesta bergväggarna i området</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1760,6 +1750,16 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">

--- a/artfynd/A 476-2025 artfynd.xlsx
+++ b/artfynd/A 476-2025 artfynd.xlsx
@@ -957,7 +957,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122009276</v>
+        <v>122008463</v>
       </c>
       <c r="B4" t="n">
         <v>74676</v>
@@ -993,17 +993,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Pers stuga, Pers stuga, Vrm</t>
+          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>364755</v>
+        <v>364847</v>
       </c>
       <c r="R4" t="n">
-        <v>6626989</v>
+        <v>6626801</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,6 +1053,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1181,7 +1206,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122008463</v>
+        <v>122009276</v>
       </c>
       <c r="B6" t="n">
         <v>74676</v>
@@ -1217,17 +1242,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
+          <t>Pers stuga, Pers stuga, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>364847</v>
+        <v>364755</v>
       </c>
       <c r="R6" t="n">
-        <v>6626801</v>
+        <v>6626989</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1256,7 +1281,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1266,7 +1291,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1277,31 +1302,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1321,7 +1321,7 @@
         <v>122025041</v>
       </c>
       <c r="B7" t="n">
-        <v>96666</v>
+        <v>96673</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122022112</v>
+        <v>122022549</v>
       </c>
       <c r="B8" t="n">
-        <v>74676</v>
+        <v>74729</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1447,25 +1447,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6426</v>
+        <v>308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>364799</v>
+        <v>364852</v>
       </c>
       <c r="R8" t="n">
-        <v>6626930</v>
+        <v>6626722</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Förekomst av kattfotslav på flera av gammal granarna, ofta i samband med gammelgranslav.</t>
+          <t>Flera torrrakor i området med förekomst av spiklavar. Blir osäker om artbestämningen. Kan vara  litenspiklav eller svartspiklav</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1542,10 +1542,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122022549</v>
+        <v>122025014</v>
       </c>
       <c r="B9" t="n">
-        <v>74729</v>
+        <v>96673</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1554,41 +1554,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>308</v>
+        <v>2569</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
+          <t>Pers stuga, Pers stuga, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>364852</v>
+        <v>364791</v>
       </c>
       <c r="R9" t="n">
-        <v>6626722</v>
+        <v>6627003</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1615,14 +1615,24 @@
           <t>2025-01-09</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-01-09</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Flera torrrakor i området med förekomst av spiklavar. Blir osäker om artbestämningen. Kan vara  litenspiklav eller svartspiklav</t>
+          <t>Växer på dom flesta bergväggarna i området</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1633,26 +1643,36 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122025014</v>
+        <v>122022112</v>
       </c>
       <c r="B10" t="n">
-        <v>96666</v>
+        <v>74676</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1665,37 +1685,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2569</v>
+        <v>6426</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Pers stuga, Pers stuga, Vrm</t>
+          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>364791</v>
+        <v>364799</v>
       </c>
       <c r="R10" t="n">
-        <v>6627003</v>
+        <v>6626930</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1722,24 +1742,14 @@
           <t>2025-01-09</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-09</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Växer på dom flesta bergväggarna i området</t>
+          <t>Förekomst av kattfotslav på flera av gammal granarna, ofta i samband med gammelgranslav.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1750,26 +1760,16 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 476-2025 artfynd.xlsx
+++ b/artfynd/A 476-2025 artfynd.xlsx
@@ -820,10 +820,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122006954</v>
+        <v>122008545</v>
       </c>
       <c r="B3" t="n">
-        <v>74676</v>
+        <v>57385</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,41 +832,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Pers stuga, Pers stuga, Vrm</t>
+          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>364824</v>
+        <v>364842</v>
       </c>
       <c r="R3" t="n">
-        <v>6626976</v>
+        <v>6626782</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -905,12 +905,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Växer på flera träd i området</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,26 +916,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -957,10 +932,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122008463</v>
+        <v>122009276</v>
       </c>
       <c r="B4" t="n">
-        <v>74676</v>
+        <v>74680</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -993,17 +968,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
+          <t>Pers stuga, Pers stuga, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>364847</v>
+        <v>364755</v>
       </c>
       <c r="R4" t="n">
-        <v>6626801</v>
+        <v>6626989</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1032,7 +1007,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1017,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,31 +1028,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1094,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122008545</v>
+        <v>122006954</v>
       </c>
       <c r="B5" t="n">
-        <v>57381</v>
+        <v>74680</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1106,41 +1056,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
+          <t>Pers stuga, Pers stuga, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>364842</v>
+        <v>364824</v>
       </c>
       <c r="R5" t="n">
-        <v>6626782</v>
+        <v>6626976</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1169,7 +1119,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1179,7 +1129,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Växer på flera träd i området</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1190,6 +1145,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1206,10 +1181,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122009276</v>
+        <v>122008463</v>
       </c>
       <c r="B6" t="n">
-        <v>74676</v>
+        <v>74680</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1242,17 +1217,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Pers stuga, Pers stuga, Vrm</t>
+          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>364755</v>
+        <v>364847</v>
       </c>
       <c r="R6" t="n">
-        <v>6626989</v>
+        <v>6626801</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1281,7 +1256,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1291,7 +1266,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1302,6 +1277,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1321,7 +1321,7 @@
         <v>122025041</v>
       </c>
       <c r="B7" t="n">
-        <v>96673</v>
+        <v>96682</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122022549</v>
+        <v>122025014</v>
       </c>
       <c r="B8" t="n">
-        <v>74729</v>
+        <v>96682</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1447,41 +1447,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>308</v>
+        <v>2569</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
+          <t>Pers stuga, Pers stuga, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>364852</v>
+        <v>364791</v>
       </c>
       <c r="R8" t="n">
-        <v>6626722</v>
+        <v>6627003</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1508,14 +1508,24 @@
           <t>2025-01-09</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-09</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Flera torrrakor i området med förekomst av spiklavar. Blir osäker om artbestämningen. Kan vara  litenspiklav eller svartspiklav</t>
+          <t>Växer på dom flesta bergväggarna i området</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1526,26 +1536,36 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122025014</v>
+        <v>122022112</v>
       </c>
       <c r="B9" t="n">
-        <v>96673</v>
+        <v>74680</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1558,37 +1578,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2569</v>
+        <v>6426</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Pers stuga, Pers stuga, Vrm</t>
+          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>364791</v>
+        <v>364799</v>
       </c>
       <c r="R9" t="n">
-        <v>6627003</v>
+        <v>6626930</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1615,24 +1635,14 @@
           <t>2025-01-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-01-09</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Växer på dom flesta bergväggarna i området</t>
+          <t>Förekomst av kattfotslav på flera av gammal granarna, ofta i samband med gammelgranslav.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1643,36 +1653,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122022112</v>
+        <v>122022549</v>
       </c>
       <c r="B10" t="n">
-        <v>74676</v>
+        <v>74733</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1681,25 +1681,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6426</v>
+        <v>308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1709,10 +1709,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>364799</v>
+        <v>364852</v>
       </c>
       <c r="R10" t="n">
-        <v>6626930</v>
+        <v>6626722</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Förekomst av kattfotslav på flera av gammal granarna, ofta i samband med gammelgranslav.</t>
+          <t>Flera torrrakor i området med förekomst av spiklavar. Blir osäker om artbestämningen. Kan vara  litenspiklav eller svartspiklav</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 476-2025 artfynd.xlsx
+++ b/artfynd/A 476-2025 artfynd.xlsx
@@ -823,7 +823,7 @@
         <v>122008545</v>
       </c>
       <c r="B3" t="n">
-        <v>57385</v>
+        <v>57388</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -932,10 +932,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122009276</v>
+        <v>122008463</v>
       </c>
       <c r="B4" t="n">
-        <v>74680</v>
+        <v>74684</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -968,17 +968,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Pers stuga, Pers stuga, Vrm</t>
+          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>364755</v>
+        <v>364847</v>
       </c>
       <c r="R4" t="n">
-        <v>6626989</v>
+        <v>6626801</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,6 +1028,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1044,10 +1069,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122006954</v>
+        <v>122009276</v>
       </c>
       <c r="B5" t="n">
-        <v>74680</v>
+        <v>74684</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1084,13 +1109,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>364824</v>
+        <v>364755</v>
       </c>
       <c r="R5" t="n">
-        <v>6626976</v>
+        <v>6626989</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,7 +1144,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,12 +1154,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Växer på flera träd i området</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,26 +1165,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1181,10 +1181,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122008463</v>
+        <v>122006954</v>
       </c>
       <c r="B6" t="n">
-        <v>74680</v>
+        <v>74684</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1217,14 +1217,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
+          <t>Pers stuga, Pers stuga, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>364847</v>
+        <v>364824</v>
       </c>
       <c r="R6" t="n">
-        <v>6626801</v>
+        <v>6626976</v>
       </c>
       <c r="S6" t="n">
         <v>9</v>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1266,7 +1266,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Växer på flera träd i området</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,11 +1283,6 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
       <c r="AJ6" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Bark of dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1318,10 +1318,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122025041</v>
+        <v>122022549</v>
       </c>
       <c r="B7" t="n">
-        <v>96682</v>
+        <v>74737</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1330,41 +1330,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2569</v>
+        <v>308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Pers stuga, Pers stuga, Vrm</t>
+          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>364825</v>
+        <v>364852</v>
       </c>
       <c r="R7" t="n">
-        <v>6626868</v>
+        <v>6626722</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1391,24 +1391,14 @@
           <t>2025-01-09</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-09</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Växer på de flesta bergsväggarna i området.</t>
+          <t>Flera torrrakor i området med förekomst av spiklavar. Blir osäker om artbestämningen. Kan vara  litenspiklav eller svartspiklav</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1423,22 +1413,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122025014</v>
+        <v>122022112</v>
       </c>
       <c r="B8" t="n">
-        <v>96682</v>
+        <v>74684</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1451,37 +1441,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2569</v>
+        <v>6426</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Pers stuga, Pers stuga, Vrm</t>
+          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>364791</v>
+        <v>364799</v>
       </c>
       <c r="R8" t="n">
-        <v>6627003</v>
+        <v>6626930</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1508,24 +1498,14 @@
           <t>2025-01-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-09</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Växer på dom flesta bergväggarna i området</t>
+          <t>Förekomst av kattfotslav på flera av gammal granarna, ofta i samband med gammelgranslav.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1536,36 +1516,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122022112</v>
+        <v>122025041</v>
       </c>
       <c r="B9" t="n">
-        <v>74680</v>
+        <v>96690</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1578,37 +1548,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6426</v>
+        <v>2569</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
+          <t>Pers stuga, Pers stuga, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>364799</v>
+        <v>364825</v>
       </c>
       <c r="R9" t="n">
-        <v>6626930</v>
+        <v>6626868</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1635,14 +1605,24 @@
           <t>2025-01-09</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-01-09</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Förekomst av kattfotslav på flera av gammal granarna, ofta i samband med gammelgranslav.</t>
+          <t>Växer på de flesta bergsväggarna i området.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1657,22 +1637,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122022549</v>
+        <v>122025014</v>
       </c>
       <c r="B10" t="n">
-        <v>74733</v>
+        <v>96690</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1681,41 +1661,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>308</v>
+        <v>2569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
+          <t>Pers stuga, Pers stuga, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>364852</v>
+        <v>364791</v>
       </c>
       <c r="R10" t="n">
-        <v>6626722</v>
+        <v>6627003</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1742,14 +1722,24 @@
           <t>2025-01-09</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-09</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Flera torrrakor i området med förekomst av spiklavar. Blir osäker om artbestämningen. Kan vara  litenspiklav eller svartspiklav</t>
+          <t>Växer på dom flesta bergväggarna i området</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1760,16 +1750,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 476-2025 artfynd.xlsx
+++ b/artfynd/A 476-2025 artfynd.xlsx
@@ -820,10 +820,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122008545</v>
+        <v>122009276</v>
       </c>
       <c r="B3" t="n">
-        <v>57388</v>
+        <v>74686</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,41 +832,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
+          <t>Pers stuga, Pers stuga, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>364842</v>
+        <v>364755</v>
       </c>
       <c r="R3" t="n">
-        <v>6626782</v>
+        <v>6626989</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,7 +935,7 @@
         <v>122008463</v>
       </c>
       <c r="B4" t="n">
-        <v>74684</v>
+        <v>74686</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1069,10 +1069,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122009276</v>
+        <v>122006954</v>
       </c>
       <c r="B5" t="n">
-        <v>74684</v>
+        <v>74686</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1109,13 +1109,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>364755</v>
+        <v>364824</v>
       </c>
       <c r="R5" t="n">
-        <v>6626989</v>
+        <v>6626976</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1154,7 +1154,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Växer på flera träd i området</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1165,6 +1170,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1181,10 +1206,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122006954</v>
+        <v>122008545</v>
       </c>
       <c r="B6" t="n">
-        <v>74684</v>
+        <v>57390</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1193,41 +1218,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Pers stuga, Pers stuga, Vrm</t>
+          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>364824</v>
+        <v>364842</v>
       </c>
       <c r="R6" t="n">
-        <v>6626976</v>
+        <v>6626782</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1256,7 +1281,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1266,12 +1291,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Växer på flera träd i området</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,26 +1302,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1321,7 +1321,7 @@
         <v>122022549</v>
       </c>
       <c r="B7" t="n">
-        <v>74737</v>
+        <v>74739</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1425,10 +1425,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122022112</v>
+        <v>122025041</v>
       </c>
       <c r="B8" t="n">
-        <v>74684</v>
+        <v>96692</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1441,37 +1441,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6426</v>
+        <v>2569</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
+          <t>Pers stuga, Pers stuga, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>364799</v>
+        <v>364825</v>
       </c>
       <c r="R8" t="n">
-        <v>6626930</v>
+        <v>6626868</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1498,14 +1498,24 @@
           <t>2025-01-09</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-09</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Förekomst av kattfotslav på flera av gammal granarna, ofta i samband med gammelgranslav.</t>
+          <t>Växer på de flesta bergsväggarna i området.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1520,22 +1530,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122025041</v>
+        <v>122025014</v>
       </c>
       <c r="B9" t="n">
-        <v>96690</v>
+        <v>96692</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1572,10 +1582,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>364825</v>
+        <v>364791</v>
       </c>
       <c r="R9" t="n">
-        <v>6626868</v>
+        <v>6627003</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1622,7 +1632,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Växer på de flesta bergsväggarna i området.</t>
+          <t>Växer på dom flesta bergväggarna i området</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1633,6 +1643,16 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1649,10 +1669,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122025014</v>
+        <v>122022112</v>
       </c>
       <c r="B10" t="n">
-        <v>96690</v>
+        <v>74686</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1665,37 +1685,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2569</v>
+        <v>6426</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Pers stuga, Pers stuga, Vrm</t>
+          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>364791</v>
+        <v>364799</v>
       </c>
       <c r="R10" t="n">
-        <v>6627003</v>
+        <v>6626930</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1722,24 +1742,14 @@
           <t>2025-01-09</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-09</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Växer på dom flesta bergväggarna i området</t>
+          <t>Förekomst av kattfotslav på flera av gammal granarna, ofta i samband med gammelgranslav.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1750,26 +1760,16 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 476-2025 artfynd.xlsx
+++ b/artfynd/A 476-2025 artfynd.xlsx
@@ -820,7 +820,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122009276</v>
+        <v>122006954</v>
       </c>
       <c r="B3" t="n">
         <v>74686</v>
@@ -860,13 +860,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>364755</v>
+        <v>364824</v>
       </c>
       <c r="R3" t="n">
-        <v>6626989</v>
+        <v>6626976</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -905,7 +905,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Växer på flera träd i området</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,6 +921,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -932,7 +957,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122008463</v>
+        <v>122009276</v>
       </c>
       <c r="B4" t="n">
         <v>74686</v>
@@ -968,17 +993,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
+          <t>Pers stuga, Pers stuga, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>364847</v>
+        <v>364755</v>
       </c>
       <c r="R4" t="n">
-        <v>6626801</v>
+        <v>6626989</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1007,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1017,7 +1042,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,31 +1053,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1069,10 +1069,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122006954</v>
+        <v>122008545</v>
       </c>
       <c r="B5" t="n">
-        <v>74686</v>
+        <v>57390</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1081,41 +1081,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Pers stuga, Pers stuga, Vrm</t>
+          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>364824</v>
+        <v>364842</v>
       </c>
       <c r="R5" t="n">
-        <v>6626976</v>
+        <v>6626782</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1154,12 +1154,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Växer på flera träd i området</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1170,26 +1165,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1206,10 +1181,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122008545</v>
+        <v>122008463</v>
       </c>
       <c r="B6" t="n">
-        <v>57390</v>
+        <v>74686</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1218,25 +1193,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1246,13 +1221,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>364842</v>
+        <v>364847</v>
       </c>
       <c r="R6" t="n">
-        <v>6626782</v>
+        <v>6626801</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1281,7 +1256,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1291,7 +1266,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1302,6 +1277,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1425,10 +1425,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122025041</v>
+        <v>122022112</v>
       </c>
       <c r="B8" t="n">
-        <v>96692</v>
+        <v>74686</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1441,37 +1441,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2569</v>
+        <v>6426</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Pers stuga, Pers stuga, Vrm</t>
+          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>364825</v>
+        <v>364799</v>
       </c>
       <c r="R8" t="n">
-        <v>6626868</v>
+        <v>6626930</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1498,24 +1498,14 @@
           <t>2025-01-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-09</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Växer på de flesta bergsväggarna i området.</t>
+          <t>Förekomst av kattfotslav på flera av gammal granarna, ofta i samband med gammelgranslav.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1530,12 +1520,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1669,10 +1659,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122022112</v>
+        <v>122025041</v>
       </c>
       <c r="B10" t="n">
-        <v>74686</v>
+        <v>96692</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1685,37 +1675,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6426</v>
+        <v>2569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
+          <t>Pers stuga, Pers stuga, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>364799</v>
+        <v>364825</v>
       </c>
       <c r="R10" t="n">
-        <v>6626930</v>
+        <v>6626868</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1742,14 +1732,24 @@
           <t>2025-01-09</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-09</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Förekomst av kattfotslav på flera av gammal granarna, ofta i samband med gammelgranslav.</t>
+          <t>Växer på de flesta bergsväggarna i området.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1764,12 +1764,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 476-2025 artfynd.xlsx
+++ b/artfynd/A 476-2025 artfynd.xlsx
@@ -820,10 +820,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122008463</v>
+        <v>122008545</v>
       </c>
       <c r="B3" t="n">
-        <v>74686</v>
+        <v>57390</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,25 +832,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -860,13 +860,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>364847</v>
+        <v>364842</v>
       </c>
       <c r="R3" t="n">
-        <v>6626801</v>
+        <v>6626782</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,31 +916,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -957,10 +932,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122008545</v>
+        <v>122008463</v>
       </c>
       <c r="B4" t="n">
-        <v>57390</v>
+        <v>74686</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -969,25 +944,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -997,13 +972,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>364842</v>
+        <v>364847</v>
       </c>
       <c r="R4" t="n">
-        <v>6626782</v>
+        <v>6626801</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1032,7 +1007,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1017,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,6 +1028,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1318,10 +1318,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122022112</v>
+        <v>122025041</v>
       </c>
       <c r="B7" t="n">
-        <v>74686</v>
+        <v>96708</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1334,37 +1334,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>2569</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
+          <t>Pers stuga, Pers stuga, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>364799</v>
+        <v>364825</v>
       </c>
       <c r="R7" t="n">
-        <v>6626930</v>
+        <v>6626868</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1391,14 +1391,24 @@
           <t>2025-01-09</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-09</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Förekomst av kattfotslav på flera av gammal granarna, ofta i samband med gammelgranslav.</t>
+          <t>Växer på de flesta bergsväggarna i området.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1413,22 +1423,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122022549</v>
+        <v>122022112</v>
       </c>
       <c r="B8" t="n">
-        <v>74739</v>
+        <v>74686</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1437,25 +1447,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>308</v>
+        <v>6426</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1465,10 +1475,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>364852</v>
+        <v>364799</v>
       </c>
       <c r="R8" t="n">
-        <v>6626722</v>
+        <v>6626930</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1505,7 +1515,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Flera torrrakor i området med förekomst av spiklavar. Blir osäker om artbestämningen. Kan vara  litenspiklav eller svartspiklav</t>
+          <t>Förekomst av kattfotslav på flera av gammal granarna, ofta i samband med gammelgranslav.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1532,10 +1542,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122025041</v>
+        <v>122022549</v>
       </c>
       <c r="B9" t="n">
-        <v>96708</v>
+        <v>74739</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1544,41 +1554,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2569</v>
+        <v>308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Pers stuga, Pers stuga, Vrm</t>
+          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>364825</v>
+        <v>364852</v>
       </c>
       <c r="R9" t="n">
-        <v>6626868</v>
+        <v>6626722</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1605,24 +1615,14 @@
           <t>2025-01-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-01-09</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Växer på de flesta bergsväggarna i området.</t>
+          <t>Flera torrrakor i området med förekomst av spiklavar. Blir osäker om artbestämningen. Kan vara  litenspiklav eller svartspiklav</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1637,12 +1637,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 476-2025 artfynd.xlsx
+++ b/artfynd/A 476-2025 artfynd.xlsx
@@ -820,10 +820,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122008545</v>
+        <v>122008463</v>
       </c>
       <c r="B3" t="n">
-        <v>57390</v>
+        <v>74686</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,25 +832,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -860,13 +860,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>364842</v>
+        <v>364847</v>
       </c>
       <c r="R3" t="n">
-        <v>6626782</v>
+        <v>6626801</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,6 +916,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -932,7 +957,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122008463</v>
+        <v>122006954</v>
       </c>
       <c r="B4" t="n">
         <v>74686</v>
@@ -968,14 +993,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
+          <t>Pers stuga, Pers stuga, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>364847</v>
+        <v>364824</v>
       </c>
       <c r="R4" t="n">
-        <v>6626801</v>
+        <v>6626976</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -1007,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1017,7 +1042,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Växer på flera träd i området</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,11 +1059,6 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
       <c r="AJ4" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1046,12 +1071,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Bark of dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1069,10 +1094,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122006954</v>
+        <v>122008545</v>
       </c>
       <c r="B5" t="n">
-        <v>74686</v>
+        <v>57390</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1081,41 +1106,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Pers stuga, Pers stuga, Vrm</t>
+          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>364824</v>
+        <v>364842</v>
       </c>
       <c r="R5" t="n">
-        <v>6626976</v>
+        <v>6626782</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1144,7 +1169,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1154,12 +1179,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Växer på flera träd i området</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1170,26 +1190,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1318,10 +1318,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122025041</v>
+        <v>122025014</v>
       </c>
       <c r="B7" t="n">
-        <v>96708</v>
+        <v>96718</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1358,10 +1358,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>364825</v>
+        <v>364791</v>
       </c>
       <c r="R7" t="n">
-        <v>6626868</v>
+        <v>6627003</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Växer på de flesta bergsväggarna i området.</t>
+          <t>Växer på dom flesta bergväggarna i området</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1419,6 +1419,16 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1435,10 +1445,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122022112</v>
+        <v>122025041</v>
       </c>
       <c r="B8" t="n">
-        <v>74686</v>
+        <v>96718</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1451,37 +1461,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6426</v>
+        <v>2569</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
+          <t>Pers stuga, Pers stuga, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>364799</v>
+        <v>364825</v>
       </c>
       <c r="R8" t="n">
-        <v>6626930</v>
+        <v>6626868</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1508,14 +1518,24 @@
           <t>2025-01-09</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-09</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Förekomst av kattfotslav på flera av gammal granarna, ofta i samband med gammelgranslav.</t>
+          <t>Växer på de flesta bergsväggarna i området.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1530,22 +1550,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122022549</v>
+        <v>122022112</v>
       </c>
       <c r="B9" t="n">
-        <v>74739</v>
+        <v>74686</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1554,25 +1574,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>308</v>
+        <v>6426</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1582,10 +1602,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>364852</v>
+        <v>364799</v>
       </c>
       <c r="R9" t="n">
-        <v>6626722</v>
+        <v>6626930</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1622,7 +1642,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Flera torrrakor i området med förekomst av spiklavar. Blir osäker om artbestämningen. Kan vara  litenspiklav eller svartspiklav</t>
+          <t>Förekomst av kattfotslav på flera av gammal granarna, ofta i samband med gammelgranslav.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1649,10 +1669,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122025014</v>
+        <v>122022549</v>
       </c>
       <c r="B10" t="n">
-        <v>96708</v>
+        <v>74739</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1661,41 +1681,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2569</v>
+        <v>308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Pers stuga, Pers stuga, Vrm</t>
+          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>364791</v>
+        <v>364852</v>
       </c>
       <c r="R10" t="n">
-        <v>6627003</v>
+        <v>6626722</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1722,24 +1742,14 @@
           <t>2025-01-09</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-09</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Växer på dom flesta bergväggarna i området</t>
+          <t>Flera torrrakor i området med förekomst av spiklavar. Blir osäker om artbestämningen. Kan vara  litenspiklav eller svartspiklav</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1750,26 +1760,16 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 476-2025 artfynd.xlsx
+++ b/artfynd/A 476-2025 artfynd.xlsx
@@ -957,10 +957,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122006954</v>
+        <v>122008545</v>
       </c>
       <c r="B4" t="n">
-        <v>74686</v>
+        <v>57390</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -969,41 +969,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Pers stuga, Pers stuga, Vrm</t>
+          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>364824</v>
+        <v>364842</v>
       </c>
       <c r="R4" t="n">
-        <v>6626976</v>
+        <v>6626782</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,12 +1042,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Växer på flera träd i området</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1058,26 +1053,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1094,10 +1069,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122008545</v>
+        <v>122009276</v>
       </c>
       <c r="B5" t="n">
-        <v>57390</v>
+        <v>74686</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1106,41 +1081,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
+          <t>Pers stuga, Pers stuga, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>364842</v>
+        <v>364755</v>
       </c>
       <c r="R5" t="n">
-        <v>6626782</v>
+        <v>6626989</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1169,7 +1144,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1179,7 +1154,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1206,7 +1181,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122009276</v>
+        <v>122006954</v>
       </c>
       <c r="B6" t="n">
         <v>74686</v>
@@ -1246,13 +1221,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>364755</v>
+        <v>364824</v>
       </c>
       <c r="R6" t="n">
-        <v>6626989</v>
+        <v>6626976</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1281,7 +1256,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1291,7 +1266,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Växer på flera träd i området</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1302,6 +1282,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1318,10 +1318,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122025014</v>
+        <v>122022549</v>
       </c>
       <c r="B7" t="n">
-        <v>96718</v>
+        <v>74739</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1330,41 +1330,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2569</v>
+        <v>308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Pers stuga, Pers stuga, Vrm</t>
+          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>364791</v>
+        <v>364852</v>
       </c>
       <c r="R7" t="n">
-        <v>6627003</v>
+        <v>6626722</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1391,24 +1391,14 @@
           <t>2025-01-09</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-09</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Växer på dom flesta bergväggarna i området</t>
+          <t>Flera torrrakor i området med förekomst av spiklavar. Blir osäker om artbestämningen. Kan vara  litenspiklav eller svartspiklav</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1419,26 +1409,16 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1562,10 +1542,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122022112</v>
+        <v>122025014</v>
       </c>
       <c r="B9" t="n">
-        <v>74686</v>
+        <v>96718</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1578,37 +1558,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6426</v>
+        <v>2569</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
+          <t>Pers stuga, Pers stuga, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>364799</v>
+        <v>364791</v>
       </c>
       <c r="R9" t="n">
-        <v>6626930</v>
+        <v>6627003</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1635,14 +1615,24 @@
           <t>2025-01-09</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-01-09</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Förekomst av kattfotslav på flera av gammal granarna, ofta i samband med gammelgranslav.</t>
+          <t>Växer på dom flesta bergväggarna i området</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1653,26 +1643,36 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122022549</v>
+        <v>122022112</v>
       </c>
       <c r="B10" t="n">
-        <v>74739</v>
+        <v>74686</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1681,25 +1681,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>308</v>
+        <v>6426</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1709,10 +1709,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>364852</v>
+        <v>364799</v>
       </c>
       <c r="R10" t="n">
-        <v>6626722</v>
+        <v>6626930</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Flera torrrakor i området med förekomst av spiklavar. Blir osäker om artbestämningen. Kan vara  litenspiklav eller svartspiklav</t>
+          <t>Förekomst av kattfotslav på flera av gammal granarna, ofta i samband med gammelgranslav.</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 476-2025 artfynd.xlsx
+++ b/artfynd/A 476-2025 artfynd.xlsx
@@ -823,7 +823,7 @@
         <v>122008463</v>
       </c>
       <c r="B3" t="n">
-        <v>74686</v>
+        <v>74691</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -957,10 +957,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122008545</v>
+        <v>122009276</v>
       </c>
       <c r="B4" t="n">
-        <v>57390</v>
+        <v>74691</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -969,41 +969,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
+          <t>Pers stuga, Pers stuga, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>364842</v>
+        <v>364755</v>
       </c>
       <c r="R4" t="n">
-        <v>6626782</v>
+        <v>6626989</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1069,10 +1069,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122009276</v>
+        <v>122006954</v>
       </c>
       <c r="B5" t="n">
-        <v>74686</v>
+        <v>74691</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1109,13 +1109,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>364755</v>
+        <v>364824</v>
       </c>
       <c r="R5" t="n">
-        <v>6626989</v>
+        <v>6626976</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1154,7 +1154,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Växer på flera träd i området</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1165,6 +1170,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1181,10 +1206,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122006954</v>
+        <v>122008545</v>
       </c>
       <c r="B6" t="n">
-        <v>74686</v>
+        <v>57395</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1193,41 +1218,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Pers stuga, Pers stuga, Vrm</t>
+          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>364824</v>
+        <v>364842</v>
       </c>
       <c r="R6" t="n">
-        <v>6626976</v>
+        <v>6626782</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1256,7 +1281,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1266,12 +1291,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:49</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Växer på flera träd i området</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,26 +1302,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1321,7 +1321,7 @@
         <v>122022549</v>
       </c>
       <c r="B7" t="n">
-        <v>74739</v>
+        <v>74744</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>122025041</v>
       </c>
       <c r="B8" t="n">
-        <v>96718</v>
+        <v>96730</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>122025014</v>
       </c>
       <c r="B9" t="n">
-        <v>96718</v>
+        <v>96730</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>122022112</v>
       </c>
       <c r="B10" t="n">
-        <v>74686</v>
+        <v>74691</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 476-2025 artfynd.xlsx
+++ b/artfynd/A 476-2025 artfynd.xlsx
@@ -820,10 +820,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122008463</v>
+        <v>122008545</v>
       </c>
       <c r="B3" t="n">
-        <v>74691</v>
+        <v>57395</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,25 +832,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -860,13 +860,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>364847</v>
+        <v>364842</v>
       </c>
       <c r="R3" t="n">
-        <v>6626801</v>
+        <v>6626782</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,31 +916,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -957,7 +932,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122009276</v>
+        <v>122008463</v>
       </c>
       <c r="B4" t="n">
         <v>74691</v>
@@ -993,17 +968,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Pers stuga, Pers stuga, Vrm</t>
+          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>364755</v>
+        <v>364847</v>
       </c>
       <c r="R4" t="n">
-        <v>6626989</v>
+        <v>6626801</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1032,7 +1007,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1017,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,6 +1028,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1206,10 +1206,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122008545</v>
+        <v>122009276</v>
       </c>
       <c r="B6" t="n">
-        <v>57395</v>
+        <v>74691</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1218,41 +1218,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
+          <t>Pers stuga, Pers stuga, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>364842</v>
+        <v>364755</v>
       </c>
       <c r="R6" t="n">
-        <v>6626782</v>
+        <v>6626989</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1318,10 +1318,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122022549</v>
+        <v>122025014</v>
       </c>
       <c r="B7" t="n">
-        <v>74744</v>
+        <v>96735</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1330,41 +1330,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>308</v>
+        <v>2569</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
+          <t>Pers stuga, Pers stuga, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>364852</v>
+        <v>364791</v>
       </c>
       <c r="R7" t="n">
-        <v>6626722</v>
+        <v>6627003</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1391,14 +1391,24 @@
           <t>2025-01-09</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-01-09</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Flera torrrakor i området med förekomst av spiklavar. Blir osäker om artbestämningen. Kan vara  litenspiklav eller svartspiklav</t>
+          <t>Växer på dom flesta bergväggarna i området</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1409,26 +1419,36 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Isabel Gunn</t>
+          <t>Petrus Oledal</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122025041</v>
+        <v>122022112</v>
       </c>
       <c r="B8" t="n">
-        <v>96730</v>
+        <v>74691</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1441,37 +1461,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2569</v>
+        <v>6426</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Pers stuga, Pers stuga, Vrm</t>
+          <t>Kollerudsbäcken, Kollerudsbäcken, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>364825</v>
+        <v>364799</v>
       </c>
       <c r="R8" t="n">
-        <v>6626868</v>
+        <v>6626930</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1498,24 +1518,14 @@
           <t>2025-01-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-09</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Växer på de flesta bergsväggarna i området.</t>
+          <t>Förekomst av kattfotslav på flera av gammal granarna, ofta i samband med gammelgranslav.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1530,22 +1540,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Petrus Oledal</t>
+          <t>Isabel Gunn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122025014</v>
+        <v>122025041</v>
       </c>
       <c r="B9" t="n">
-        <v>96730</v>
+        <v>96735</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1582,10 +1592,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>364791</v>
+        <v>364825</v>
       </c>
       <c r="R9" t="n">
-        <v>6627003</v>
+        <v>6626868</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1632,7 +1642,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Växer på dom flesta bergväggarna i området</t>
+          <t>Växer på de flesta bergsväggarna i området.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1643,16 +1653,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1669,10 +1669,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122022112</v>
+        <v>122022549</v>
       </c>
       <c r="B10" t="n">
-        <v>74691</v>
+        <v>74744</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1681,25 +1681,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6426</v>
+        <v>308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1709,10 +1709,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>364799</v>
+        <v>364852</v>
       </c>
       <c r="R10" t="n">
-        <v>6626930</v>
+        <v>6626722</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Förekomst av kattfotslav på flera av gammal granarna, ofta i samband med gammelgranslav.</t>
+          <t>Flera torrrakor i området med förekomst av spiklavar. Blir osäker om artbestämningen. Kan vara  litenspiklav eller svartspiklav</t>
         </is>
       </c>
       <c r="AD10" t="b">
